--- a/The Complete Financial Analyst Course/Section 5/50. Key Excel Functions COUNT, COUNTA, COUNTIF,/Lecture-Count-Countif-Countifs-Unsolved (1).xlsx
+++ b/The Complete Financial Analyst Course/Section 5/50. Key Excel Functions COUNT, COUNTA, COUNTIF,/Lecture-Count-Countif-Countifs-Unsolved (1).xlsx
@@ -1,25 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NewPC\Desktop\Courses\Video creating\The Complete Financial Analyst Course\Resources\5. Beginner, Intermediate &amp; Advanced Functions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\economics\udemy_economics\The Complete Financial Analyst Course\Section 5\50. Key Excel Functions COUNT, COUNTA, COUNTIF,\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D3BD96-0042-43EF-8F03-C3A87D0B6386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="2"/>
+    <workbookView xWindow="28680" yWindow="270" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Count" sheetId="1" r:id="rId1"/>
     <sheet name="Countif" sheetId="2" r:id="rId2"/>
     <sheet name="Countifs" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -97,7 +109,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -168,16 +180,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -496,8 +504,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:F16"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="2" customWidth="1"/>
@@ -509,12 +517,12 @@
     <col min="7" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -531,7 +539,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
@@ -548,7 +556,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
@@ -565,7 +573,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
@@ -582,7 +590,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
@@ -599,7 +607,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
@@ -616,7 +624,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
@@ -633,7 +641,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
@@ -650,7 +658,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
@@ -667,7 +675,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>19</v>
       </c>
@@ -684,23 +692,27 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="6"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B14" s="2">
+        <f>COUNTA(B4:B13)</f>
+        <v>9</v>
+      </c>
+      <c r="E14" s="4">
+        <f>COUNT(E4:E12)</f>
+        <v>9</v>
+      </c>
+      <c r="F14" s="2">
+        <f>COUNTIF(F4:F12, "&gt;60")</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F15" s="2">
+        <f>COUNTIFS(F4:F12,"&gt;60",D4:D12,"YES")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -712,8 +724,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:H14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="B1:F14"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="2" customWidth="1"/>
@@ -725,12 +737,12 @@
     <col min="7" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -747,7 +759,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
@@ -764,7 +776,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
@@ -781,7 +793,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
@@ -798,7 +810,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
@@ -815,7 +827,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
@@ -832,7 +844,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
@@ -849,7 +861,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
@@ -866,7 +878,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
@@ -883,7 +895,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>19</v>
       </c>
@@ -900,17 +912,8 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="F14" s="7"/>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F14" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -918,7 +921,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:F14"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1106,15 +1109,8 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-    </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F14" s="7"/>
+      <c r="F14" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
